--- a/AAII_Financials/Quarterly/ARE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
   <si>
     <t>ARE</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>663200</v>
+      </c>
+      <c r="E8" s="3">
         <v>670900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>754100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>752100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>753000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>757700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>795600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>791700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>766900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>769300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>757600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>714000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>714100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>701000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>674700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>684100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1310600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>638200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>576900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>547800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>989500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>479800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>463700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>545000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>437000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>439900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>408100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>390500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>373900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>358800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>340500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>341800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>645200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>320100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>298800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>285400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>273100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>270900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>249200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>230400</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>207300</v>
+      </c>
+      <c r="E9" s="3">
         <v>224100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>232500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>239200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>224400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>226400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>240400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>233300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>217300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>218300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>222700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>217700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>211800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>206900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>204400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>201200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>377600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>181300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>175700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>166000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>281800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>137900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>136800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>140400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>123900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>129100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>121900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>116500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>105700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>101500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>97700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>99800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>183700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>91800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>88100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>83500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>77000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>77100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>73200</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>72000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>455900</v>
+      </c>
+      <c r="E10" s="3">
         <v>446700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>521600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>512900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>528600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>531300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>555100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>558500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>549600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>550900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>534900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>496300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>502200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>494100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>470300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>482900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>933000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>456900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>401200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>381800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>707700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>341900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>326900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>404600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>313100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>310800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>286200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>274100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>268200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>257300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>242800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>242000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>461500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>228300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>210700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>201900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>196100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>193800</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>176000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>158400</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,252 +1496,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-356400</v>
+        <v>222500</v>
       </c>
       <c r="E14" s="3">
+        <v>-360900</v>
+      </c>
+      <c r="F14" s="3">
         <v>1101200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>314600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>160200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>69000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>137900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-21400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>74400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>201000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>101300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>32000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>45100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>26200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>38800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3300</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>42600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>77300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>72400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>33100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>60500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>13200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>12300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>40200</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>7400</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>1100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>6300</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>2800</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>200</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>700</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>16000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>304400</v>
+      </c>
+      <c r="E15" s="3">
         <v>305400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>322100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>340200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>346100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>342100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>330100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>294000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>290700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>287600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>285200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>269400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>273600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>265300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>264500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>254900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>482700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>240700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>239300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>210800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>371000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>180900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>177800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>176800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>168000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>175500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>140500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>135600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>134400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>134100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>125000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>119600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>233100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>114200</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>107700</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>107800</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>104100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>97200</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>95200</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>77100</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>548600</v>
+      </c>
+      <c r="E17" s="3">
         <v>564300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>582600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>608700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>599700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>599100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>603300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>571200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>552600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>552900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>567300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>533000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>531300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>520400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>538000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>544900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>948000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>462900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>456600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>457400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>802000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>425200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>380300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>414600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>336900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>338600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>304500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>320200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>266600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>267600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>245100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>243100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>468400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>228400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>217500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>208900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>200500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>194200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>201900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>176300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>114600</v>
+      </c>
+      <c r="E18" s="3">
         <v>106600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>171500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>143500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>153300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>158500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>192300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>220500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>214300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>216300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>190300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>181000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>182800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>180600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>136700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>139200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>362600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>175300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>120300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>90400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>187500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>54600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>83400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>130400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>100100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>101300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>103600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>70300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>107300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>91200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>95400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>98700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>176800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>91700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>81300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>76500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>72600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>76700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>47300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2096,452 +2130,464 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>-23900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>267200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-116900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-263200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>14400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>69700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>314200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>7400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>411300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>8800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>188500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-24900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>157900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-60100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>22700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>84700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-73800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>162900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>100300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>86700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>14100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>3800</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>419000</v>
+      </c>
+      <c r="E21" s="3">
         <v>412000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>493500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>483700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>499500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>500600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>522400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>514500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>505000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>503900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>475600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>450400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>456400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>445900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>377300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>661400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>728400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>152700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>373900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>371000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>872600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>242900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>672400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>315900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>456600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>251900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>402100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>145800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>264500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>310000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>146600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>381200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>510100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>292700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>189400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>198400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>177300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>174500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>146200</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>131500</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>64300</v>
+      </c>
+      <c r="E22" s="3">
         <v>64600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>65700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>54900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>55300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>50900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>55700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>43600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>45800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>40800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>32000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>17100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>13800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>17500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>23000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>53700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>29400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>34900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>35700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>71600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>36500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>37500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>43300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>45000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>45700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>45500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>46200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>42900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>39100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>40200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>42200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>75000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>36900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>36100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>31000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>31700</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>29800</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>31200</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>25900</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E23" s="3">
         <v>398400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-995400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-197800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-62200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>38700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>213600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>94000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>219200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-42700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>68300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>133700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>121700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>95300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>383400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>192000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-117400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>99800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>124400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>430100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>25500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>457100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>95800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>243600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>30700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>216100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-36000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>87200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>136800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-18600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>219400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>202100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>141500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>45600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>59500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>41500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>47600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>19800</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>28500</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2584,8 +2630,8 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2662,8 +2708,11 @@
       <c r="AP24" s="3">
         <v>0</v>
       </c>
+      <c r="AQ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E26" s="3">
         <v>398400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-995400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-197800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-62200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>38700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>213600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>94000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>219200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-42700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>68300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>133700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>121700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>95300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>383400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>192000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-117400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>99800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>124400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>430100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>25500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>457100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>95800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>243600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>30700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>216100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-36000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>87200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>136800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-18600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>219400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>202100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>141500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>45600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>59500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>41500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>47600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>19800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>28500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>358900</v>
+        <v>-73700</v>
       </c>
       <c r="E27" s="3">
+        <v>360400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1081800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-234900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-109600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-64900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>164700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>42900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>166900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-91900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>21900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>87300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>75300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>51800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>341400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>120000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-150800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>72800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>101300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>389300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>8000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>436600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>79300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>226600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>18200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>200600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-49800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>76300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>123900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-30100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>208900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>185100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>133000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>36800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>51300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>31600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>25700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-25100</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,208 +3630,214 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>23900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-267200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>116900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>263200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-14400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-69700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-314200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-411300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-8800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-188500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>24900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-157900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>60100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-22700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-84700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>73800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-162900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-100300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-86700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-14100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-3800</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="E33" s="3">
         <v>361700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1080900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-232800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-107000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-62200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>167900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>46700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>170500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-88400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>24300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>89900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>77900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>51800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>341400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>120000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-150800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>72800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>101300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>389300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>8000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>436600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>79300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>226600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>18200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>200600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-49800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>76300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>123900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-30100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>208900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>185100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>133000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>36800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>51300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>31600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>25700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-25100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="E35" s="3">
         <v>361700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1080900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-232800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-107000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-62200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>167900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>46700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>170500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-88400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>24300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>89900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>77900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>51800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>341400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>120000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-150800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>72800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>101300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>389300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>8000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>436600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>79300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>226600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>18200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>200600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-49800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>76300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>123900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-30100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>208900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>185100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>133000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>36800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>51300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>31600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>25700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-25100</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>470400</v>
+      </c>
+      <c r="E41" s="3">
         <v>418700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>549100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>579500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>520500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>476400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>552100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>562600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>561000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>722200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>618200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>532400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>924400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1263500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>825200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>533800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>420300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>775100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>361300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>325900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>323900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>492200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>568500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>446300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>206900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>445300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>189700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>410700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>198900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>261400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>234200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>204200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>287000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>221600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>254400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>118600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>124900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>151200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>125000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>157900</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,130 +4553,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1546900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1527000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1503100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1542200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1516000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1490800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1355500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1281000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1254600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1203200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1114500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1075100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1046600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1044700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>15000</v>
-      </c>
-      <c r="AC43" s="3">
-        <v>10700</v>
       </c>
       <c r="AD43" s="3">
         <v>10700</v>
       </c>
       <c r="AE43" s="3">
+        <v>10700</v>
+      </c>
+      <c r="AF43" s="3">
         <v>9200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>10200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>10300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>11600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>9300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>11900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>10300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>9900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>8400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>10000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>9700</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,53 +4803,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E45" s="3">
         <v>92800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>62300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>76200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>56900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>93500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>55300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>71300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>49300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>81400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>56800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>70600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>63500</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4829,53 +4928,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2077400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2043200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2119200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2202600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2100800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2068000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1970700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1931900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1869700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2016200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1832100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1713500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2034200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2406500</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,357 +5053,366 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1714600</v>
+      </c>
+      <c r="E47" s="3">
         <v>1566900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1531900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1577200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1516900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1529800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1516900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1559500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1534900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1552200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1487300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1469500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1533800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1611400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1925700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1934000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1964200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2145300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2360500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2781900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2732100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2227400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2202800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1920500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1904300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1707700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1527800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1370800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1432000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1330700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1168900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1194300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1022500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>932700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>633900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>519000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>483000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>444900</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>392700</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>454600</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29563500</v>
+      </c>
+      <c r="E48" s="3">
         <v>29240200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>29031800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32651700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32751600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32822000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32682700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33906700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33359800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33008800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32321300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32415300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>31884000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>31614900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>30675400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>29506400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>28695700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>27839500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>25632800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>23647000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>22271800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20808800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>18613000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>18104000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>16750600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>16316900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>15306100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>14091900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13281700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12776900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12009500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>11671400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>11259200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>10724900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>10298000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>10046500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>9819400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>9470700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>9078000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>7939200</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>178500</v>
+      </c>
+      <c r="E49" s="3">
         <v>189100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>204000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>235300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>255200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>280400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>305100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>373800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>398000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>426700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>461600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>492700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>524500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>589800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>615600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>638000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>683300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>729800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>609900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>632100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>595500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>550400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>462300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>451000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>312900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>337800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>281700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>186800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>158600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>157200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>150300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>157700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>152400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>107600</v>
       </c>
-      <c r="AK49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL49" s="3" t="s">
         <v>8</v>
       </c>
@@ -5317,8 +5428,11 @@
       <c r="AP49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>609800</v>
+      </c>
+      <c r="E52" s="3">
         <v>634600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>697200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>161300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>463700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>364300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>517100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>147900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>138700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>145500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>128800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>147300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>127500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>131800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1585300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1853900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1572800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1560800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1379100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1279300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1219900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1211800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1147400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1145800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1053700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1041200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1011500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>960800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>921500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>911200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>856200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>833600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>799400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>779800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>679000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>638300</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>605000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>585300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>548200</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>526500</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>34632200</v>
+      </c>
+      <c r="E54" s="3">
         <v>34167400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>34081800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>37375100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>37623600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>37600400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>37527400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>38488100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37847900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>37699000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36771400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36783300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36659300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>36912500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>35523400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>34368600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>33244100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32844300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>30219400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>28558700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>27018900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>25234300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>22827900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>21910700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>20069100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>19701900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>18390500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>17058200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>16039500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>15480200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>14465000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>14105600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>13562200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12821200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12104000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>11545300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>11245700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>10868600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>10354900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>9293900</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,180 +6145,184 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>394000</v>
+      </c>
+      <c r="E57" s="3">
         <v>368100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>510600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>514900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>407000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>383000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>534800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>470000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>434700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>432300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>524400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>516400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>366400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>354900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>389700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>458800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>428500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>389100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>513400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>558100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>305600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>320300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>285000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>318300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>233700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>243000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>474800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>491700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>430700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>453200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>491400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>445900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>394400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>370200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>349900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>338300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>327400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>391000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>366200</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>269900</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>359700</v>
+      </c>
+      <c r="E58" s="3">
         <v>2066700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>672600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>649600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>660100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>899600</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>10900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17300</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>5400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>18300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -6259,175 +6393,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>130500</v>
+      </c>
+      <c r="E59" s="3">
         <v>128900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>127800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>230600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>229700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>228600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>230300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>227200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>227400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>222100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>221800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>214500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>214600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>209300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1240300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1209100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1171200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1059800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1057500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>957100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>901500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>829400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>830000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>743200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>657500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>669900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>398100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>386200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>358000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>355000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>110300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>101100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>98700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>93100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>92100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>83400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>81600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>79000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>76900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>66700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>884200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2563700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1310900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1395100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1296700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1511100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>765100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>697200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>672900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>671700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>746300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>736200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>591700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>582600</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,252 +6643,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12808100</v>
+      </c>
+      <c r="E61" s="3">
         <v>10811900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12088500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>13306000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12997400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12562700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12751500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13339900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12792400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12581500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11698500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11582400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11559200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11924100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10159800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10525800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10271400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10303200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8791900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9263600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8841000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8540900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7563300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7823200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7523300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7305100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6777500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6737700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6356200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5843500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5478300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5684000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5614100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5210800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4764800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>4817000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>4775400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>4560700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>4164000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>4329100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>557600</v>
+      </c>
+      <c r="E62" s="3">
         <v>551500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>635000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>665600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>687700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>782400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>909100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1083700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1119800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1114800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1139900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1233000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1223500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1238100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>52700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>54400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>56500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>65500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>59800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>58700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>58200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>51100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>47100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>48100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>29600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>15600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>14000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>14200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>14600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>10300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>13200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>7000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>7400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>7500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>8000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>4300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>3100</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15456900</v>
+      </c>
+      <c r="E66" s="3">
         <v>14803700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14925400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16256900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15884600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15600900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15129000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15784700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15181000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14943100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14148400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14070400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13892000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14225700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16551000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16752300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16104700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15914300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14029800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13835500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12827800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>12243900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11102200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11208900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10637700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10379300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9524700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9267900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8410500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7913600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7123000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7232800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7101700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6626600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6154300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6138400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>6088500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>5916200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>5459100</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>5383800</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7607,7 +7775,7 @@
         <v>0</v>
       </c>
       <c r="AD70" s="3">
-        <v>57500</v>
+        <v>0</v>
       </c>
       <c r="AE70" s="3">
         <v>57500</v>
@@ -7616,10 +7784,10 @@
         <v>57500</v>
       </c>
       <c r="AG70" s="3">
+        <v>57500</v>
+      </c>
+      <c r="AH70" s="3">
         <v>64300</v>
-      </c>
-      <c r="AH70" s="3">
-        <v>74400</v>
       </c>
       <c r="AI70" s="3">
         <v>74400</v>
@@ -7640,13 +7808,16 @@
         <v>74400</v>
       </c>
       <c r="AO70" s="3">
+        <v>74400</v>
+      </c>
+      <c r="AP70" s="3">
         <v>216900</v>
       </c>
-      <c r="AP70" s="3">
+      <c r="AQ70" s="3">
         <v>291800</v>
       </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,8 +7938,11 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7811,8 +7985,8 @@
       <c r="P72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
+      <c r="Q72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R72" s="3">
         <v>0</v>
@@ -7889,8 +8063,11 @@
       <c r="AP72" s="3">
         <v>0</v>
       </c>
+      <c r="AQ72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15554000</v>
+      </c>
+      <c r="E76" s="3">
         <v>15734100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15470100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16639300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17175200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17464600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17889000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18217600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18258600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18412600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18471200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18627900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18797400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18884000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18972400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17616300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17139300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16930000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16189500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14723200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14191000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12990400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11725700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10701800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9431400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9322600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8865800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7732800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7571600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7509100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7277600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6798400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6386100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6120200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5875300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5332600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>5082800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4878000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>4678900</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>3618300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="E81" s="3">
         <v>361700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1080900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-232800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-107000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-62200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>167900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>46700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>170500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-88400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>24300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>89900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>77900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>51800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>341400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>120000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-150800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>72800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>101300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>389300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>8000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>436600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>79300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>226600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>18200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>200600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-49800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>76300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>123900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-30100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>208900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>185100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>133000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>36800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>51300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>31600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>25700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-25100</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>335900</v>
+      </c>
+      <c r="E83" s="3">
         <v>342100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>221400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>276700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>268200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>287600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>124600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>246100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>248800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>265300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>95000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>231400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>225300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>240700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>264500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>254900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>482700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>240700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>239300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>210800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>371000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>180900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>177800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>176800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>168000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>175500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>140500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>135600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>134400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>134100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>125000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>119600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>233100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>114200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>107700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>107800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>104100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>97200</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>95200</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>77100</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>337000</v>
+      </c>
+      <c r="E89" s="3">
         <v>196600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>312400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>433500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>460200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>207900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>274200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>477400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>411800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>341200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>428600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>417900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>478500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>305600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>401200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>363000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>530100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>191100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>249600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>308800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>451800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>212100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>173600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>315300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>202400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>191300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>178300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>197200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>171600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>136700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>156300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>155800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>258200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>128900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>93600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>133500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>116100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>107600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>100700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>119700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,8 +9910,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9734,86 +9955,89 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1361400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1263500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-990100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2570200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2223600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1351500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1002000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-465400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-373100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-372200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-326400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-373500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-309800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-337400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-336300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-241000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-263500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-232500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-431200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-206400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-84700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-154500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-218700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-872200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-902900</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-293600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-409700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-584800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1799600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-407900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-374900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-654800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>446300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-488500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-573600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-894900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-390100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-676500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-394400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1039700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1359800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-624400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3096200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2488800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1673900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1296900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4136500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2437900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-413100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1468000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-563500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-833600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1290500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-898600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-717900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-734300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-397600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-495300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1268900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-598000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-423400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-332000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-513400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-468400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-781300</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-341300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10231,121 +10465,124 @@
         <v>123800</v>
       </c>
       <c r="E96" s="3">
+        <v>123800</v>
+      </c>
+      <c r="F96" s="3">
         <v>227000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>227200</v>
       </c>
       <c r="G96" s="3">
         <v>227200</v>
       </c>
       <c r="H96" s="3">
+        <v>227200</v>
+      </c>
+      <c r="I96" s="3">
         <v>230000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>227200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>227400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>222100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>221800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>214500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>214600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>209300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>209100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-193600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-192600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-371500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-183800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-173600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-170600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-311800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-151000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-143000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-133700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-130000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-126300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-114600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-113500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-109600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-109300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-100000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-97600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-183000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-91100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-82300</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-80500</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-75600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-73700</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>-62400</v>
       </c>
       <c r="AP96" s="3">
         <v>-62400</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-62400</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E100" s="3">
         <v>258000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2144600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>30800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-40700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>370800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-738700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>24900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>624400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>55200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-133600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-422300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1174800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>950700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>610100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2668900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2752600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1473600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>998700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3444100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2162300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>351600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1395800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>113300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>889700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>901800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>916500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>468400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>640800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>280600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>251300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1056500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>451300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>460500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>199100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>372100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>388700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>647800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>124200</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-300</v>
       </c>
       <c r="M101" s="3">
         <v>-300</v>
       </c>
       <c r="N101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>200</v>
       </c>
-      <c r="AO101" s="3">
-        <v>0</v>
-      </c>
       <c r="AP101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ101" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-130400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-30400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>56200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>44200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-76100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-19800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-165800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>70900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>93100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-392600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-338100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>440400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>348500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>102400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>454900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>47200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>10500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-240100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-63300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>112700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>243500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-246800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>245700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-210300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>214700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-77600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>43700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>38300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-88000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>44700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-18200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>130900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-24700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>28200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-32900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-98100</v>
       </c>
     </row>
